--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_345_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_345_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3176</v>
+        <v>4.7833</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0617</v>
+        <v>5.5508</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2559</v>
+        <v>-0.7675</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8327</v>
+        <v>2.1898</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8222</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0106</v>
+        <v>1.3384</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6089</v>
+        <v>3.3838</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1735</v>
+        <v>0.9915</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4354</v>
+        <v>2.3923</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7761</v>
+        <v>-1.1941</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3513</v>
+        <v>-0.1401</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4248</v>
+        <v>-1.0539</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>3.575</v>
+        <v>1.0574</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4708</v>
+        <v>0.4169</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1043</v>
+        <v>0.6405</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3295</v>
+        <v>4.0364</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6937</v>
+        <v>2.3854</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3642</v>
+        <v>1.651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1898</v>
+        <v>1.8327</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8222</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3384</v>
+        <v>1.0106</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3838</v>
+        <v>2.6089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9915</v>
+        <v>1.1735</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3923</v>
+        <v>1.4354</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1941</v>
+        <v>-0.7761</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1401</v>
+        <v>-0.3513</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0539</v>
+        <v>-0.4248</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6036</v>
+        <v>2.2938</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4402</v>
+        <v>0.7945</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0438</v>
+        <v>1.4993</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5977</v>
+        <v>3.1168</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7619</v>
+        <v>2.0309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8358</v>
+        <v>1.0859</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8617</v>
+        <v>2.1999</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7182</v>
+        <v>2.0962</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8566</v>
+        <v>0.1038</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2859</v>
+        <v>2.9545</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0391</v>
+        <v>2.2687</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7532</v>
+        <v>0.6859</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5758</v>
+        <v>-0.7546</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3209</v>
+        <v>-0.1725</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8966</v>
+        <v>-0.5821</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7635</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8338</v>
+        <v>0.2361</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0703</v>
+        <v>0.6807</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.377</v>
+        <v>2.6381</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0559</v>
+        <v>1.6006</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3211</v>
+        <v>1.0375</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1999</v>
+        <v>-0.8617</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0962</v>
+        <v>-1.7182</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1038</v>
+        <v>0.8566</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9545</v>
+        <v>-0.2859</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2687</v>
+        <v>-2.0391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6859</v>
+        <v>1.7532</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7546</v>
+        <v>-0.5758</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1725</v>
+        <v>0.3209</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5821</v>
+        <v>-0.8966</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.177</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>0.6726</v>
       </c>
       <c r="U5" t="n">
-        <v>0.916</v>
+        <v>0.1314</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2395</v>
+        <v>1.3106</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4678</v>
+        <v>-1.1086</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7718</v>
+        <v>2.4192</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4858</v>
+        <v>-0.1093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1344</v>
+        <v>-1.8558</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3513</v>
+        <v>1.7465</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0571</v>
+        <v>-0.8808</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0203</v>
+        <v>-1.7373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4287</v>
+        <v>0.7715</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1141</v>
+        <v>-0.1186</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>0.8901</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0785</v>
+        <v>-0.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1993</v>
+        <v>-0.2278</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1208</v>
+        <v>0.1658</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7886</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0514</v>
+        <v>1.0609</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0653</v>
+        <v>0.6804</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1168</v>
+        <v>0.3805</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1093</v>
+        <v>0.1026</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8558</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7465</v>
+        <v>-0.6993</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8808</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7373</v>
+        <v>1.3276</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7715</v>
+        <v>-0.4755</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1186</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8901</v>
+        <v>0.0502</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3211</v>
+        <v>0.4944</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>0.1024</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1366</v>
+        <v>0.3921</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9869</v>
+        <v>1.0537</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8416</v>
+        <v>1.5122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1453</v>
+        <v>-0.4585</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1026</v>
+        <v>5.0622</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8018999999999999</v>
+        <v>-0.5688</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6993</v>
+        <v>5.631</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5780999999999999</v>
+        <v>5.4915</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3276</v>
+        <v>-0.5644</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>6.0559</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4755</v>
+        <v>-0.4293</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0502</v>
+        <v>-0.4248</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-4.639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4204</v>
+        <v>1.1666</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2636</v>
+        <v>0.7472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1568</v>
+        <v>0.4193</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6361</v>
+        <v>0.337</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5987</v>
+        <v>-0.4012</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9626</v>
+        <v>0.7382</v>
       </c>
       <c r="G9" t="n">
-        <v>5.0622</v>
+        <v>0.4858</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5688</v>
+        <v>0.1344</v>
       </c>
       <c r="I9" t="n">
-        <v>5.631</v>
+        <v>0.3513</v>
       </c>
       <c r="J9" t="n">
-        <v>5.4915</v>
+        <v>0.0571</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5644</v>
+        <v>0.0203</v>
       </c>
       <c r="L9" t="n">
-        <v>6.0559</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4293</v>
+        <v>0.4287</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0044</v>
+        <v>0.1141</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4248</v>
+        <v>0.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.749</v>
+        <v>0.1759</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8338</v>
+        <v>0.3304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0848</v>
+        <v>-0.1544</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7219</v>
+        <v>-1.041</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2323</v>
+        <v>-1.6858</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5104</v>
+        <v>0.6448</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2704</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7556</v>
+        <v>-0.0747</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>0.1731</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7351</v>
+        <v>-1.6598</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4998</v>
+        <v>-3.1892</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7647</v>
+        <v>1.5295</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1812</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1419</v>
+        <v>0.2172</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0351</v>
+        <v>0.2754</v>
       </c>
       <c r="U11" t="n">
-        <v>0.177</v>
+        <v>-0.0582</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5661</v>
+        <v>-2.0031</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5724</v>
+        <v>-2.1438</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0062</v>
+        <v>0.1407</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1972</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.673</v>
+        <v>-0.11</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4481</v>
+        <v>-0.0196</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.5126</v>
+        <v>13.6329</v>
       </c>
       <c r="E13" t="n">
-        <v>4.111499999999999</v>
+        <v>5.231699999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>8.401199999999999</v>
+        <v>8.401300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>8.253199999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9478999999999997</v>
+        <v>-0.9479000000000002</v>
       </c>
       <c r="I13" t="n">
         <v>9.2012</v>
@@ -1468,13 +1468,13 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7592</v>
+        <v>6.8794</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3811</v>
+        <v>3.501199999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3783</v>
+        <v>3.378200000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.8197000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7201</v>
+        <v>2.0796</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7429</v>
+        <v>3.0352</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0228</v>
+        <v>-0.9556</v>
       </c>
       <c r="G14" t="n">
         <v>1.3345</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6175</v>
+        <v>0.977</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3645</v>
+        <v>0.6567</v>
       </c>
       <c r="U14" t="n">
-        <v>0.253</v>
+        <v>0.3203</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5738</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0324</v>
+        <v>-0.3863</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6062</v>
+        <v>0.8979</v>
       </c>
       <c r="G15" t="n">
         <v>1.5534</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2838</v>
+        <v>-0.3459</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4955</v>
+        <v>0.1417</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7793</v>
+        <v>-0.4876</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1475</v>
+        <v>0.2628</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8292</v>
+        <v>-1.4754</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6817</v>
+        <v>1.7381</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2425</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6241</v>
+        <v>-1.2138</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3364</v>
+        <v>-0.9825</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2877</v>
+        <v>-0.2313</v>
       </c>
       <c r="V16" t="n">
         <v>2.2551</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7071</v>
+        <v>-0.3805</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0346</v>
+        <v>0.4372</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6725</v>
+        <v>-0.8177</v>
       </c>
       <c r="G17" t="n">
         <v>0.2762</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4652</v>
+        <v>-0.1386</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>-0.0431</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0496</v>
+        <v>-0.0955</v>
       </c>
       <c r="V17" t="n">
         <v>-1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.78</v>
+        <v>-0.9759</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9957</v>
+        <v>-2.1137</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2157</v>
+        <v>1.1377</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9164</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6726</v>
+        <v>0.4766</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2517</v>
+        <v>0.1737</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9124</v>
+        <v>-1.5756</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0348</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0646</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4714</v>
+        <v>-0.1346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1726</v>
+        <v>-0.0718</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4125</v>
+        <v>-2.136</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0416</v>
+        <v>0.659</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3709</v>
+        <v>-2.795</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4063</v>
+        <v>0.4855</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2603</v>
+        <v>0.2245</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6667</v>
+        <v>0.261</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8176</v>
+        <v>2.8911</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9046</v>
+        <v>0.7331</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0871</v>
+        <v>2.1581</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2239</v>
+        <v>-2.4056</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6443</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5796</v>
+        <v>-1.897</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.702</v>
+        <v>-1.9204</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6994</v>
+        <v>-1.3559</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0026</v>
+        <v>-0.5645</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8608</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7143</v>
+        <v>-2.4632</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3052</v>
+        <v>-1.1595</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0195</v>
+        <v>-1.3037</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4855</v>
+        <v>-2.4063</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2245</v>
+        <v>0.2603</v>
       </c>
       <c r="I21" t="n">
-        <v>0.261</v>
+        <v>-2.6667</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8911</v>
+        <v>0.8176</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7331</v>
+        <v>0.9046</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1581</v>
+        <v>-0.0871</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4056</v>
+        <v>-3.2239</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.6443</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.897</v>
+        <v>-2.5796</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4987</v>
+        <v>-0.7527</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.7098</v>
+        <v>-0.8173</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.789</v>
+        <v>0.0646</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8608</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1043</v>
+        <v>-3.3041</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7952</v>
+        <v>-3.2532</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3091</v>
+        <v>-0.0509</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1549</v>
+        <v>-2.1181</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3916</v>
+        <v>-0.8031</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7632</v>
+        <v>-1.3149</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5393</v>
+        <v>-0.0378</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.3053</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.2676</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6156</v>
+        <v>-2.0803</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4547</v>
+        <v>-0.4978</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1609</v>
+        <v>-1.5825</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06850000000000001</v>
+        <v>-1.3484</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3857</v>
+        <v>-0.896</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3172</v>
+        <v>-0.4525</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0283</v>
+        <v>-3.7448</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.843</v>
+        <v>-3.5029</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1853</v>
+        <v>-0.2419</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1181</v>
+        <v>-3.1549</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8031</v>
+        <v>-1.3916</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3149</v>
+        <v>-1.7632</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0378</v>
+        <v>-1.5393</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3053</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2676</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0803</v>
+        <v>-1.6156</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4978</v>
+        <v>-0.4547</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5825</v>
+        <v>-1.1609</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0726</v>
+        <v>-0.572</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4857</v>
+        <v>-0.322</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5869</v>
+        <v>-0.25</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.5125</v>
+        <v>-11.7261</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.4011</v>
+        <v>-8.401199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.111299999999999</v>
+        <v>-3.3251</v>
       </c>
       <c r="G24" t="n">
         <v>-8.2532</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9481000000000003</v>
+        <v>0.9481000000000002</v>
       </c>
       <c r="I24" t="n">
         <v>-9.2012</v>
@@ -2326,16 +2326,16 @@
         <v>12.7575</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7592</v>
+        <v>-4.9728</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.378400000000001</v>
+        <v>-3.3783</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.381</v>
+        <v>-1.5946</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8196999999999998</v>
+        <v>-0.8196999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>2.5698</v>
